--- a/Data/EXCEL/Transfer/salemon/202206/6541-salemon-202206.xlsx
+++ b/Data/EXCEL/Transfer/salemon/202206/6541-salemon-202206.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" mc:Ignorable="x15 xr xr6 xr10">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="25225"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="25330"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\linea\OneDrive\myStocksPGMs\V2.0\xls2xlsx\transfer\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WORKSPACES\myStocksPGMs\V2.0\xls2xlsx\transfer\202206\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{DDF53B59-E7F6-45E8-9030-8D90CB2CCE8A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{AD1387CF-86CA-4240-B598-2A1BCC949137}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3285" yWindow="2625" windowWidth="24465" windowHeight="12855"/>
+    <workbookView xWindow="945" yWindow="3600" windowWidth="26925" windowHeight="11205"/>
   </bookViews>
   <sheets>
     <sheet name="6541-salemon-202206" sheetId="2" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="664" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="668" uniqueCount="18">
   <si>
     <t>月別</t>
   </si>
@@ -261,7 +261,7 @@
     </font>
     <font>
       <sz val="10"/>
-      <color rgb="FF008000"/>
+      <color rgb="FFFF0000"/>
       <name val="新細明體"/>
       <family val="2"/>
       <charset val="136"/>
@@ -277,7 +277,7 @@
     </font>
     <font>
       <sz val="10"/>
-      <color rgb="FFFF0000"/>
+      <color rgb="FF008000"/>
       <name val="新細明體"/>
       <family val="2"/>
       <charset val="136"/>
@@ -1218,20 +1218,20 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:Q87"/>
+  <dimension ref="A1:Q88"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="12.625" customWidth="1"/>
-    <col min="2" max="5" width="10.625" customWidth="1"/>
-    <col min="6" max="7" width="11.625" customWidth="1"/>
-    <col min="8" max="8" width="12.125" customWidth="1"/>
-    <col min="9" max="9" width="10.625" customWidth="1"/>
-    <col min="10" max="10" width="10.125" customWidth="1"/>
-    <col min="11" max="13" width="12.125" customWidth="1"/>
-    <col min="14" max="14" width="10.625" customWidth="1"/>
-    <col min="15" max="15" width="10.125" customWidth="1"/>
-    <col min="16" max="16" width="12.125" customWidth="1"/>
-    <col min="17" max="17" width="13.75" customWidth="1"/>
+    <col min="1" max="1" width="13.875" customWidth="1"/>
+    <col min="2" max="5" width="11.625" customWidth="1"/>
+    <col min="6" max="7" width="12.75" customWidth="1"/>
+    <col min="8" max="8" width="13.25" customWidth="1"/>
+    <col min="9" max="9" width="11.625" customWidth="1"/>
+    <col min="10" max="10" width="11.125" customWidth="1"/>
+    <col min="11" max="13" width="13.25" customWidth="1"/>
+    <col min="14" max="14" width="11.625" customWidth="1"/>
+    <col min="15" max="15" width="11.125" customWidth="1"/>
+    <col min="16" max="16" width="13.25" customWidth="1"/>
+    <col min="17" max="17" width="14.625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:17" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
@@ -1384,52 +1384,52 @@
     </row>
     <row r="5" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A5" s="6">
-        <v>44682</v>
+        <v>44713</v>
       </c>
       <c r="B5" s="7">
-        <v>55.8</v>
+        <v>55</v>
       </c>
       <c r="C5" s="7">
-        <v>55.2</v>
+        <v>67.3</v>
       </c>
       <c r="D5" s="7">
-        <v>61.2</v>
+        <v>73.3</v>
       </c>
       <c r="E5" s="7">
         <v>52</v>
       </c>
       <c r="F5" s="8">
-        <v>-0.5</v>
+        <v>12.1</v>
       </c>
       <c r="G5" s="8">
-        <v>-0.9</v>
+        <v>21.92</v>
       </c>
       <c r="H5" s="9">
-        <v>6.7000000000000002E-3</v>
+        <v>0.01</v>
       </c>
       <c r="I5" s="8">
-        <v>-51.4</v>
+        <v>49.6</v>
       </c>
       <c r="J5" s="9" t="s">
         <v>17</v>
       </c>
       <c r="K5" s="9">
-        <v>5.1700000000000003E-2</v>
+        <v>6.1699999999999998E-2</v>
       </c>
       <c r="L5" s="9" t="s">
         <v>17</v>
       </c>
       <c r="M5" s="9">
-        <v>6.7000000000000002E-3</v>
+        <v>0.01</v>
       </c>
       <c r="N5" s="8">
-        <v>-51.4</v>
+        <v>49.6</v>
       </c>
       <c r="O5" s="9" t="s">
         <v>17</v>
       </c>
       <c r="P5" s="9">
-        <v>5.1700000000000003E-2</v>
+        <v>6.1699999999999998E-2</v>
       </c>
       <c r="Q5" s="9" t="s">
         <v>17</v>
@@ -1437,52 +1437,52 @@
     </row>
     <row r="6" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A6" s="6">
-        <v>44652</v>
+        <v>44682</v>
       </c>
       <c r="B6" s="7">
-        <v>54.9</v>
+        <v>55.8</v>
       </c>
       <c r="C6" s="7">
-        <v>55.7</v>
+        <v>55.2</v>
       </c>
       <c r="D6" s="7">
-        <v>62.4</v>
+        <v>61.2</v>
       </c>
       <c r="E6" s="7">
-        <v>53.7</v>
+        <v>52</v>
       </c>
       <c r="F6" s="10">
-        <v>0.3</v>
+        <v>-0.5</v>
       </c>
       <c r="G6" s="10">
-        <v>0.54</v>
+        <v>-0.9</v>
       </c>
       <c r="H6" s="9">
-        <v>1.38E-2</v>
-      </c>
-      <c r="I6" s="9">
-        <v>0</v>
+        <v>6.7000000000000002E-3</v>
+      </c>
+      <c r="I6" s="10">
+        <v>-51.4</v>
       </c>
       <c r="J6" s="9" t="s">
         <v>17</v>
       </c>
       <c r="K6" s="9">
-        <v>4.4999999999999998E-2</v>
+        <v>5.1700000000000003E-2</v>
       </c>
       <c r="L6" s="9" t="s">
         <v>17</v>
       </c>
       <c r="M6" s="9">
-        <v>1.38E-2</v>
-      </c>
-      <c r="N6" s="9">
-        <v>0</v>
+        <v>6.7000000000000002E-3</v>
+      </c>
+      <c r="N6" s="10">
+        <v>-51.4</v>
       </c>
       <c r="O6" s="9" t="s">
         <v>17</v>
       </c>
       <c r="P6" s="9">
-        <v>4.4999999999999998E-2</v>
+        <v>5.1700000000000003E-2</v>
       </c>
       <c r="Q6" s="9" t="s">
         <v>17</v>
@@ -1490,37 +1490,37 @@
     </row>
     <row r="7" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A7" s="6">
-        <v>44621</v>
+        <v>44652</v>
       </c>
       <c r="B7" s="7">
-        <v>59.6</v>
+        <v>54.9</v>
       </c>
       <c r="C7" s="7">
-        <v>55.4</v>
+        <v>55.7</v>
       </c>
       <c r="D7" s="7">
-        <v>60.5</v>
+        <v>62.4</v>
       </c>
       <c r="E7" s="7">
-        <v>52.4</v>
+        <v>53.7</v>
       </c>
       <c r="F7" s="8">
-        <v>-3.6</v>
+        <v>0.3</v>
       </c>
       <c r="G7" s="8">
-        <v>-6.1</v>
+        <v>0.54</v>
       </c>
       <c r="H7" s="9">
         <v>1.38E-2</v>
       </c>
-      <c r="I7" s="10">
-        <v>64.2</v>
+      <c r="I7" s="9">
+        <v>0</v>
       </c>
       <c r="J7" s="9" t="s">
         <v>17</v>
       </c>
       <c r="K7" s="9">
-        <v>3.1199999999999999E-2</v>
+        <v>4.4999999999999998E-2</v>
       </c>
       <c r="L7" s="9" t="s">
         <v>17</v>
@@ -1528,14 +1528,14 @@
       <c r="M7" s="9">
         <v>1.38E-2</v>
       </c>
-      <c r="N7" s="10">
-        <v>64.2</v>
+      <c r="N7" s="9">
+        <v>0</v>
       </c>
       <c r="O7" s="9" t="s">
         <v>17</v>
       </c>
       <c r="P7" s="9">
-        <v>3.1199999999999999E-2</v>
+        <v>4.4999999999999998E-2</v>
       </c>
       <c r="Q7" s="9" t="s">
         <v>17</v>
@@ -1543,52 +1543,52 @@
     </row>
     <row r="8" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A8" s="6">
-        <v>44593</v>
+        <v>44621</v>
       </c>
       <c r="B8" s="7">
-        <v>54.5</v>
+        <v>59.6</v>
       </c>
       <c r="C8" s="7">
-        <v>59</v>
+        <v>55.4</v>
       </c>
       <c r="D8" s="7">
-        <v>63</v>
+        <v>60.5</v>
       </c>
       <c r="E8" s="7">
-        <v>54</v>
+        <v>52.4</v>
       </c>
       <c r="F8" s="10">
-        <v>5.8</v>
+        <v>-3.6</v>
       </c>
       <c r="G8" s="10">
-        <v>10.9</v>
+        <v>-6.1</v>
       </c>
       <c r="H8" s="9">
-        <v>8.3999999999999995E-3</v>
+        <v>1.38E-2</v>
       </c>
       <c r="I8" s="8">
-        <v>-8.01</v>
+        <v>64.2</v>
       </c>
       <c r="J8" s="9" t="s">
         <v>17</v>
       </c>
       <c r="K8" s="9">
-        <v>1.7500000000000002E-2</v>
+        <v>3.1199999999999999E-2</v>
       </c>
       <c r="L8" s="9" t="s">
         <v>17</v>
       </c>
       <c r="M8" s="9">
-        <v>8.3999999999999995E-3</v>
+        <v>1.38E-2</v>
       </c>
       <c r="N8" s="8">
-        <v>-8.01</v>
+        <v>64.2</v>
       </c>
       <c r="O8" s="9" t="s">
         <v>17</v>
       </c>
       <c r="P8" s="9">
-        <v>1.7500000000000002E-2</v>
+        <v>3.1199999999999999E-2</v>
       </c>
       <c r="Q8" s="9" t="s">
         <v>17</v>
@@ -1596,52 +1596,52 @@
     </row>
     <row r="9" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A9" s="6">
-        <v>44562</v>
+        <v>44593</v>
       </c>
       <c r="B9" s="7">
-        <v>58.5</v>
+        <v>54.5</v>
       </c>
       <c r="C9" s="7">
-        <v>53.2</v>
+        <v>59</v>
       </c>
       <c r="D9" s="7">
         <v>63</v>
       </c>
       <c r="E9" s="7">
-        <v>51.3</v>
+        <v>54</v>
       </c>
       <c r="F9" s="8">
-        <v>-4.9000000000000004</v>
+        <v>5.8</v>
       </c>
       <c r="G9" s="8">
-        <v>-8.43</v>
+        <v>10.9</v>
       </c>
       <c r="H9" s="9">
-        <v>9.1000000000000004E-3</v>
-      </c>
-      <c r="I9" s="8">
-        <v>-29.2</v>
+        <v>8.3999999999999995E-3</v>
+      </c>
+      <c r="I9" s="10">
+        <v>-8.01</v>
       </c>
       <c r="J9" s="9" t="s">
         <v>17</v>
       </c>
       <c r="K9" s="9">
-        <v>9.1000000000000004E-3</v>
+        <v>1.7500000000000002E-2</v>
       </c>
       <c r="L9" s="9" t="s">
         <v>17</v>
       </c>
       <c r="M9" s="9">
-        <v>9.1000000000000004E-3</v>
-      </c>
-      <c r="N9" s="8">
-        <v>-29.2</v>
+        <v>8.3999999999999995E-3</v>
+      </c>
+      <c r="N9" s="10">
+        <v>-8.01</v>
       </c>
       <c r="O9" s="9" t="s">
         <v>17</v>
       </c>
       <c r="P9" s="9">
-        <v>9.1000000000000004E-3</v>
+        <v>1.7500000000000002E-2</v>
       </c>
       <c r="Q9" s="9" t="s">
         <v>17</v>
@@ -1649,243 +1649,243 @@
     </row>
     <row r="10" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A10" s="6">
-        <v>44531</v>
+        <v>44562</v>
       </c>
       <c r="B10" s="7">
-        <v>52.4</v>
+        <v>58.5</v>
       </c>
       <c r="C10" s="7">
-        <v>58.1</v>
+        <v>53.2</v>
       </c>
       <c r="D10" s="7">
-        <v>81.8</v>
+        <v>63</v>
       </c>
       <c r="E10" s="7">
-        <v>52</v>
+        <v>51.3</v>
       </c>
       <c r="F10" s="10">
-        <v>5.8</v>
+        <v>-4.9000000000000004</v>
       </c>
       <c r="G10" s="10">
-        <v>11.09</v>
+        <v>-8.43</v>
       </c>
       <c r="H10" s="9">
-        <v>1.29E-2</v>
+        <v>9.1000000000000004E-3</v>
       </c>
       <c r="I10" s="10">
-        <v>120.6</v>
+        <v>-29.2</v>
       </c>
       <c r="J10" s="9" t="s">
         <v>17</v>
       </c>
       <c r="K10" s="9">
-        <v>5.4100000000000002E-2</v>
-      </c>
-      <c r="L10" s="10">
-        <v>1702</v>
+        <v>9.1000000000000004E-3</v>
+      </c>
+      <c r="L10" s="9" t="s">
+        <v>17</v>
       </c>
       <c r="M10" s="9">
-        <v>1.29E-2</v>
+        <v>9.1000000000000004E-3</v>
       </c>
       <c r="N10" s="10">
-        <v>120.6</v>
+        <v>-29.2</v>
       </c>
       <c r="O10" s="9" t="s">
         <v>17</v>
       </c>
       <c r="P10" s="9">
-        <v>5.4100000000000002E-2</v>
-      </c>
-      <c r="Q10" s="10">
-        <v>1702</v>
+        <v>9.1000000000000004E-3</v>
+      </c>
+      <c r="Q10" s="9" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="11" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A11" s="6">
-        <v>44501</v>
+        <v>44531</v>
       </c>
       <c r="B11" s="7">
-        <v>51.4</v>
+        <v>52.4</v>
       </c>
       <c r="C11" s="7">
-        <v>52.3</v>
+        <v>58.1</v>
       </c>
       <c r="D11" s="7">
-        <v>54.9</v>
+        <v>81.8</v>
       </c>
       <c r="E11" s="7">
-        <v>48.35</v>
-      </c>
-      <c r="F11" s="10">
-        <v>0.8</v>
-      </c>
-      <c r="G11" s="10">
-        <v>1.55</v>
+        <v>52</v>
+      </c>
+      <c r="F11" s="8">
+        <v>5.8</v>
+      </c>
+      <c r="G11" s="8">
+        <v>11.09</v>
       </c>
       <c r="H11" s="9">
-        <v>5.7999999999999996E-3</v>
+        <v>1.29E-2</v>
       </c>
       <c r="I11" s="8">
-        <v>-80.400000000000006</v>
+        <v>120.6</v>
       </c>
       <c r="J11" s="9" t="s">
         <v>17</v>
       </c>
       <c r="K11" s="9">
-        <v>4.1200000000000001E-2</v>
-      </c>
-      <c r="L11" s="10">
-        <v>1273.3</v>
+        <v>5.4100000000000002E-2</v>
+      </c>
+      <c r="L11" s="8">
+        <v>1702</v>
       </c>
       <c r="M11" s="9">
-        <v>5.7999999999999996E-3</v>
+        <v>1.29E-2</v>
       </c>
       <c r="N11" s="8">
-        <v>-80.400000000000006</v>
+        <v>120.6</v>
       </c>
       <c r="O11" s="9" t="s">
         <v>17</v>
       </c>
       <c r="P11" s="9">
-        <v>4.1200000000000001E-2</v>
-      </c>
-      <c r="Q11" s="10">
-        <v>1273.3</v>
+        <v>5.4100000000000002E-2</v>
+      </c>
+      <c r="Q11" s="8">
+        <v>1702</v>
       </c>
     </row>
     <row r="12" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A12" s="6">
-        <v>44470</v>
+        <v>44501</v>
       </c>
       <c r="B12" s="7">
-        <v>44.9</v>
+        <v>51.4</v>
       </c>
       <c r="C12" s="7">
-        <v>51.5</v>
+        <v>52.3</v>
       </c>
       <c r="D12" s="7">
-        <v>58</v>
+        <v>54.9</v>
       </c>
       <c r="E12" s="7">
-        <v>41.65</v>
-      </c>
-      <c r="F12" s="10">
-        <v>6.1</v>
-      </c>
-      <c r="G12" s="10">
-        <v>13.44</v>
+        <v>48.35</v>
+      </c>
+      <c r="F12" s="8">
+        <v>0.8</v>
+      </c>
+      <c r="G12" s="8">
+        <v>1.55</v>
       </c>
       <c r="H12" s="9">
-        <v>2.98E-2</v>
-      </c>
-      <c r="I12" s="9" t="s">
-        <v>17</v>
+        <v>5.7999999999999996E-3</v>
+      </c>
+      <c r="I12" s="10">
+        <v>-80.400000000000006</v>
       </c>
       <c r="J12" s="9" t="s">
         <v>17</v>
       </c>
       <c r="K12" s="9">
-        <v>3.5400000000000001E-2</v>
-      </c>
-      <c r="L12" s="10">
-        <v>1079</v>
+        <v>4.1200000000000001E-2</v>
+      </c>
+      <c r="L12" s="8">
+        <v>1273.3</v>
       </c>
       <c r="M12" s="9">
-        <v>2.98E-2</v>
-      </c>
-      <c r="N12" s="9" t="s">
-        <v>17</v>
+        <v>5.7999999999999996E-3</v>
+      </c>
+      <c r="N12" s="10">
+        <v>-80.400000000000006</v>
       </c>
       <c r="O12" s="9" t="s">
         <v>17</v>
       </c>
       <c r="P12" s="9">
-        <v>3.5400000000000001E-2</v>
-      </c>
-      <c r="Q12" s="10">
-        <v>1079</v>
+        <v>4.1200000000000001E-2</v>
+      </c>
+      <c r="Q12" s="8">
+        <v>1273.3</v>
       </c>
     </row>
     <row r="13" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A13" s="6">
-        <v>44440</v>
+        <v>44470</v>
       </c>
       <c r="B13" s="7">
-        <v>47.5</v>
+        <v>44.9</v>
       </c>
       <c r="C13" s="7">
-        <v>45.4</v>
+        <v>51.5</v>
       </c>
       <c r="D13" s="7">
-        <v>48.6</v>
+        <v>58</v>
       </c>
       <c r="E13" s="7">
-        <v>42.65</v>
+        <v>41.65</v>
       </c>
       <c r="F13" s="8">
-        <v>-2.6</v>
+        <v>6.1</v>
       </c>
       <c r="G13" s="8">
-        <v>-5.42</v>
+        <v>13.44</v>
       </c>
       <c r="H13" s="9">
-        <v>0</v>
-      </c>
-      <c r="I13" s="8">
-        <v>-100</v>
+        <v>2.98E-2</v>
+      </c>
+      <c r="I13" s="9" t="s">
+        <v>17</v>
       </c>
       <c r="J13" s="9" t="s">
         <v>17</v>
       </c>
       <c r="K13" s="9">
-        <v>5.5999999999999999E-3</v>
-      </c>
-      <c r="L13" s="10">
-        <v>86.7</v>
+        <v>3.5400000000000001E-2</v>
+      </c>
+      <c r="L13" s="8">
+        <v>1079</v>
       </c>
       <c r="M13" s="9">
-        <v>0</v>
-      </c>
-      <c r="N13" s="8">
-        <v>-100</v>
+        <v>2.98E-2</v>
+      </c>
+      <c r="N13" s="9" t="s">
+        <v>17</v>
       </c>
       <c r="O13" s="9" t="s">
         <v>17</v>
       </c>
       <c r="P13" s="9">
-        <v>5.5999999999999999E-3</v>
-      </c>
-      <c r="Q13" s="10">
-        <v>86.7</v>
+        <v>3.5400000000000001E-2</v>
+      </c>
+      <c r="Q13" s="8">
+        <v>1079</v>
       </c>
     </row>
     <row r="14" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A14" s="6">
-        <v>44409</v>
+        <v>44440</v>
       </c>
       <c r="B14" s="7">
-        <v>54</v>
+        <v>47.5</v>
       </c>
       <c r="C14" s="7">
-        <v>48</v>
+        <v>45.4</v>
       </c>
       <c r="D14" s="7">
-        <v>55.4</v>
+        <v>48.6</v>
       </c>
       <c r="E14" s="7">
-        <v>45</v>
-      </c>
-      <c r="F14" s="8">
-        <v>-5.8</v>
-      </c>
-      <c r="G14" s="8">
-        <v>-10.78</v>
+        <v>42.65</v>
+      </c>
+      <c r="F14" s="10">
+        <v>-2.6</v>
+      </c>
+      <c r="G14" s="10">
+        <v>-5.42</v>
       </c>
       <c r="H14" s="9">
-        <v>5.5999999999999999E-3</v>
-      </c>
-      <c r="I14" s="9" t="s">
-        <v>17</v>
+        <v>0</v>
+      </c>
+      <c r="I14" s="10">
+        <v>-100</v>
       </c>
       <c r="J14" s="9" t="s">
         <v>17</v>
@@ -1893,14 +1893,14 @@
       <c r="K14" s="9">
         <v>5.5999999999999999E-3</v>
       </c>
-      <c r="L14" s="10">
+      <c r="L14" s="8">
         <v>86.7</v>
       </c>
       <c r="M14" s="9">
-        <v>5.5999999999999999E-3</v>
-      </c>
-      <c r="N14" s="9" t="s">
-        <v>17</v>
+        <v>0</v>
+      </c>
+      <c r="N14" s="10">
+        <v>-100</v>
       </c>
       <c r="O14" s="9" t="s">
         <v>17</v>
@@ -1908,84 +1908,84 @@
       <c r="P14" s="9">
         <v>5.5999999999999999E-3</v>
       </c>
-      <c r="Q14" s="10">
+      <c r="Q14" s="8">
         <v>86.7</v>
       </c>
     </row>
     <row r="15" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A15" s="6">
-        <v>44378</v>
+        <v>44409</v>
       </c>
       <c r="B15" s="7">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="C15" s="7">
-        <v>53.8</v>
+        <v>48</v>
       </c>
       <c r="D15" s="7">
-        <v>59.8</v>
+        <v>55.4</v>
       </c>
       <c r="E15" s="7">
-        <v>47.35</v>
-      </c>
-      <c r="F15" s="8">
-        <v>-4.0999999999999996</v>
-      </c>
-      <c r="G15" s="8">
-        <v>-7.08</v>
+        <v>45</v>
+      </c>
+      <c r="F15" s="10">
+        <v>-5.8</v>
+      </c>
+      <c r="G15" s="10">
+        <v>-10.78</v>
       </c>
       <c r="H15" s="9">
-        <v>0</v>
+        <v>5.5999999999999999E-3</v>
       </c>
       <c r="I15" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="J15" s="8">
-        <v>-100</v>
+      <c r="J15" s="9" t="s">
+        <v>17</v>
       </c>
       <c r="K15" s="9">
-        <v>0</v>
+        <v>5.5999999999999999E-3</v>
       </c>
       <c r="L15" s="8">
-        <v>-100</v>
+        <v>86.7</v>
       </c>
       <c r="M15" s="9">
-        <v>0</v>
+        <v>5.5999999999999999E-3</v>
       </c>
       <c r="N15" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="O15" s="8">
-        <v>-100</v>
+      <c r="O15" s="9" t="s">
+        <v>17</v>
       </c>
       <c r="P15" s="9">
-        <v>0</v>
+        <v>5.5999999999999999E-3</v>
       </c>
       <c r="Q15" s="8">
-        <v>-100</v>
+        <v>86.7</v>
       </c>
     </row>
     <row r="16" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A16" s="6">
-        <v>44348</v>
+        <v>44378</v>
       </c>
       <c r="B16" s="7">
-        <v>59.1</v>
+        <v>58</v>
       </c>
       <c r="C16" s="7">
-        <v>57.9</v>
+        <v>53.8</v>
       </c>
       <c r="D16" s="7">
-        <v>63.8</v>
+        <v>59.8</v>
       </c>
       <c r="E16" s="7">
-        <v>55.8</v>
-      </c>
-      <c r="F16" s="8">
-        <v>-1</v>
-      </c>
-      <c r="G16" s="8">
-        <v>-1.7</v>
+        <v>47.35</v>
+      </c>
+      <c r="F16" s="10">
+        <v>-4.0999999999999996</v>
+      </c>
+      <c r="G16" s="10">
+        <v>-7.08</v>
       </c>
       <c r="H16" s="9">
         <v>0</v>
@@ -1993,14 +1993,14 @@
       <c r="I16" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="J16" s="9" t="s">
-        <v>17</v>
+      <c r="J16" s="10">
+        <v>-100</v>
       </c>
       <c r="K16" s="9">
         <v>0</v>
       </c>
-      <c r="L16" s="9" t="s">
-        <v>17</v>
+      <c r="L16" s="10">
+        <v>-100</v>
       </c>
       <c r="M16" s="9">
         <v>0</v>
@@ -2008,37 +2008,37 @@
       <c r="N16" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="O16" s="9" t="s">
-        <v>17</v>
+      <c r="O16" s="10">
+        <v>-100</v>
       </c>
       <c r="P16" s="9">
         <v>0</v>
       </c>
-      <c r="Q16" s="9" t="s">
-        <v>17</v>
+      <c r="Q16" s="10">
+        <v>-100</v>
       </c>
     </row>
     <row r="17" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A17" s="6">
-        <v>44317</v>
+        <v>44348</v>
       </c>
       <c r="B17" s="7">
-        <v>67.2</v>
+        <v>59.1</v>
       </c>
       <c r="C17" s="7">
-        <v>58.9</v>
+        <v>57.9</v>
       </c>
       <c r="D17" s="7">
-        <v>67.2</v>
+        <v>63.8</v>
       </c>
       <c r="E17" s="7">
-        <v>50.1</v>
-      </c>
-      <c r="F17" s="8">
-        <v>-7.8</v>
-      </c>
-      <c r="G17" s="8">
-        <v>-11.69</v>
+        <v>55.8</v>
+      </c>
+      <c r="F17" s="10">
+        <v>-1</v>
+      </c>
+      <c r="G17" s="10">
+        <v>-1.7</v>
       </c>
       <c r="H17" s="9">
         <v>0</v>
@@ -2073,25 +2073,25 @@
     </row>
     <row r="18" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A18" s="6">
-        <v>44287</v>
+        <v>44317</v>
       </c>
       <c r="B18" s="7">
-        <v>89</v>
+        <v>67.2</v>
       </c>
       <c r="C18" s="7">
-        <v>66.7</v>
+        <v>58.9</v>
       </c>
       <c r="D18" s="7">
-        <v>93.9</v>
+        <v>67.2</v>
       </c>
       <c r="E18" s="7">
-        <v>63.3</v>
-      </c>
-      <c r="F18" s="8">
-        <v>-22.3</v>
-      </c>
-      <c r="G18" s="8">
-        <v>-25.06</v>
+        <v>50.1</v>
+      </c>
+      <c r="F18" s="10">
+        <v>-7.8</v>
+      </c>
+      <c r="G18" s="10">
+        <v>-11.69</v>
       </c>
       <c r="H18" s="9">
         <v>0</v>
@@ -2126,25 +2126,25 @@
     </row>
     <row r="19" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A19" s="6">
-        <v>44256</v>
+        <v>44287</v>
       </c>
       <c r="B19" s="7">
-        <v>60</v>
+        <v>89</v>
       </c>
       <c r="C19" s="7">
-        <v>89</v>
+        <v>66.7</v>
       </c>
       <c r="D19" s="7">
-        <v>100</v>
+        <v>93.9</v>
       </c>
       <c r="E19" s="7">
-        <v>58.1</v>
+        <v>63.3</v>
       </c>
       <c r="F19" s="10">
-        <v>31.5</v>
+        <v>-22.3</v>
       </c>
       <c r="G19" s="10">
-        <v>54.78</v>
+        <v>-25.06</v>
       </c>
       <c r="H19" s="9">
         <v>0</v>
@@ -2179,25 +2179,25 @@
     </row>
     <row r="20" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A20" s="6">
-        <v>44228</v>
+        <v>44256</v>
       </c>
       <c r="B20" s="7">
-        <v>35.200000000000003</v>
+        <v>60</v>
       </c>
       <c r="C20" s="7">
-        <v>57.5</v>
+        <v>89</v>
       </c>
       <c r="D20" s="7">
-        <v>59.7</v>
+        <v>100</v>
       </c>
       <c r="E20" s="7">
-        <v>35</v>
-      </c>
-      <c r="F20" s="10">
-        <v>22.4</v>
-      </c>
-      <c r="G20" s="10">
-        <v>63.82</v>
+        <v>58.1</v>
+      </c>
+      <c r="F20" s="8">
+        <v>31.5</v>
+      </c>
+      <c r="G20" s="8">
+        <v>54.78</v>
       </c>
       <c r="H20" s="9">
         <v>0</v>
@@ -2232,25 +2232,25 @@
     </row>
     <row r="21" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A21" s="6">
-        <v>44197</v>
+        <v>44228</v>
       </c>
       <c r="B21" s="7">
-        <v>37.549999999999997</v>
+        <v>35.200000000000003</v>
       </c>
       <c r="C21" s="7">
-        <v>35.1</v>
+        <v>57.5</v>
       </c>
       <c r="D21" s="7">
-        <v>37.65</v>
+        <v>59.7</v>
       </c>
       <c r="E21" s="7">
-        <v>34.200000000000003</v>
+        <v>35</v>
       </c>
       <c r="F21" s="8">
-        <v>-2.2999999999999998</v>
+        <v>22.4</v>
       </c>
       <c r="G21" s="8">
-        <v>-6.15</v>
+        <v>63.82</v>
       </c>
       <c r="H21" s="9">
         <v>0</v>
@@ -2285,25 +2285,25 @@
     </row>
     <row r="22" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A22" s="6">
-        <v>44166</v>
+        <v>44197</v>
       </c>
       <c r="B22" s="7">
-        <v>43.45</v>
+        <v>37.549999999999997</v>
       </c>
       <c r="C22" s="7">
-        <v>37.4</v>
+        <v>35.1</v>
       </c>
       <c r="D22" s="7">
-        <v>43.5</v>
+        <v>37.65</v>
       </c>
       <c r="E22" s="7">
-        <v>36.35</v>
-      </c>
-      <c r="F22" s="8">
-        <v>-5.6</v>
-      </c>
-      <c r="G22" s="8">
-        <v>-13.02</v>
+        <v>34.200000000000003</v>
+      </c>
+      <c r="F22" s="10">
+        <v>-2.2999999999999998</v>
+      </c>
+      <c r="G22" s="10">
+        <v>-6.15</v>
       </c>
       <c r="H22" s="9">
         <v>0</v>
@@ -2315,7 +2315,7 @@
         <v>17</v>
       </c>
       <c r="K22" s="9">
-        <v>3.0000000000000001E-3</v>
+        <v>0</v>
       </c>
       <c r="L22" s="9" t="s">
         <v>17</v>
@@ -2330,7 +2330,7 @@
         <v>17</v>
       </c>
       <c r="P22" s="9">
-        <v>3.0000000000000001E-3</v>
+        <v>0</v>
       </c>
       <c r="Q22" s="9" t="s">
         <v>17</v>
@@ -2338,25 +2338,25 @@
     </row>
     <row r="23" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A23" s="6">
-        <v>44136</v>
+        <v>44166</v>
       </c>
       <c r="B23" s="7">
-        <v>37.5</v>
+        <v>43.45</v>
       </c>
       <c r="C23" s="7">
-        <v>43</v>
+        <v>37.4</v>
       </c>
       <c r="D23" s="7">
-        <v>46</v>
+        <v>43.5</v>
       </c>
       <c r="E23" s="7">
-        <v>37.1</v>
+        <v>36.35</v>
       </c>
       <c r="F23" s="10">
-        <v>5.6</v>
+        <v>-5.6</v>
       </c>
       <c r="G23" s="10">
-        <v>14.97</v>
+        <v>-13.02</v>
       </c>
       <c r="H23" s="9">
         <v>0</v>
@@ -2391,25 +2391,25 @@
     </row>
     <row r="24" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A24" s="6">
-        <v>44105</v>
+        <v>44136</v>
       </c>
       <c r="B24" s="7">
-        <v>39.5</v>
+        <v>37.5</v>
       </c>
       <c r="C24" s="7">
-        <v>37.4</v>
+        <v>43</v>
       </c>
       <c r="D24" s="7">
-        <v>41.45</v>
+        <v>46</v>
       </c>
       <c r="E24" s="7">
         <v>37.1</v>
       </c>
       <c r="F24" s="8">
-        <v>-2.6</v>
+        <v>5.6</v>
       </c>
       <c r="G24" s="8">
-        <v>-6.5</v>
+        <v>14.97</v>
       </c>
       <c r="H24" s="9">
         <v>0</v>
@@ -2444,25 +2444,25 @@
     </row>
     <row r="25" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A25" s="6">
-        <v>44075</v>
+        <v>44105</v>
       </c>
       <c r="B25" s="7">
-        <v>39.6</v>
+        <v>39.5</v>
       </c>
       <c r="C25" s="7">
-        <v>40</v>
+        <v>37.4</v>
       </c>
       <c r="D25" s="7">
-        <v>45.8</v>
+        <v>41.45</v>
       </c>
       <c r="E25" s="7">
-        <v>37.049999999999997</v>
-      </c>
-      <c r="F25" s="8">
-        <v>-0.15</v>
-      </c>
-      <c r="G25" s="8">
-        <v>-0.37</v>
+        <v>37.1</v>
+      </c>
+      <c r="F25" s="10">
+        <v>-2.6</v>
+      </c>
+      <c r="G25" s="10">
+        <v>-6.5</v>
       </c>
       <c r="H25" s="9">
         <v>0</v>
@@ -2497,31 +2497,31 @@
     </row>
     <row r="26" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A26" s="6">
-        <v>44044</v>
+        <v>44075</v>
       </c>
       <c r="B26" s="7">
-        <v>42.8</v>
+        <v>39.6</v>
       </c>
       <c r="C26" s="7">
-        <v>40.15</v>
+        <v>40</v>
       </c>
       <c r="D26" s="7">
-        <v>43.6</v>
+        <v>45.8</v>
       </c>
       <c r="E26" s="7">
-        <v>37</v>
-      </c>
-      <c r="F26" s="8">
-        <v>-2.85</v>
-      </c>
-      <c r="G26" s="8">
-        <v>-6.63</v>
+        <v>37.049999999999997</v>
+      </c>
+      <c r="F26" s="10">
+        <v>-0.15</v>
+      </c>
+      <c r="G26" s="10">
+        <v>-0.37</v>
       </c>
       <c r="H26" s="9">
         <v>0</v>
       </c>
-      <c r="I26" s="8">
-        <v>-100</v>
+      <c r="I26" s="9" t="s">
+        <v>17</v>
       </c>
       <c r="J26" s="9" t="s">
         <v>17</v>
@@ -2535,8 +2535,8 @@
       <c r="M26" s="9">
         <v>0</v>
       </c>
-      <c r="N26" s="8">
-        <v>-100</v>
+      <c r="N26" s="9" t="s">
+        <v>17</v>
       </c>
       <c r="O26" s="9" t="s">
         <v>17</v>
@@ -2550,31 +2550,31 @@
     </row>
     <row r="27" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A27" s="6">
-        <v>44013</v>
+        <v>44044</v>
       </c>
       <c r="B27" s="7">
-        <v>47.9</v>
+        <v>42.8</v>
       </c>
       <c r="C27" s="7">
-        <v>43</v>
+        <v>40.15</v>
       </c>
       <c r="D27" s="7">
-        <v>60.6</v>
+        <v>43.6</v>
       </c>
       <c r="E27" s="7">
-        <v>40.049999999999997</v>
-      </c>
-      <c r="F27" s="8">
-        <v>-4.9000000000000004</v>
-      </c>
-      <c r="G27" s="8">
-        <v>-10.23</v>
+        <v>37</v>
+      </c>
+      <c r="F27" s="10">
+        <v>-2.85</v>
+      </c>
+      <c r="G27" s="10">
+        <v>-6.63</v>
       </c>
       <c r="H27" s="9">
-        <v>3.0000000000000001E-3</v>
-      </c>
-      <c r="I27" s="9" t="s">
-        <v>17</v>
+        <v>0</v>
+      </c>
+      <c r="I27" s="10">
+        <v>-100</v>
       </c>
       <c r="J27" s="9" t="s">
         <v>17</v>
@@ -2586,10 +2586,10 @@
         <v>17</v>
       </c>
       <c r="M27" s="9">
-        <v>3.0000000000000001E-3</v>
-      </c>
-      <c r="N27" s="9" t="s">
-        <v>17</v>
+        <v>0</v>
+      </c>
+      <c r="N27" s="10">
+        <v>-100</v>
       </c>
       <c r="O27" s="9" t="s">
         <v>17</v>
@@ -2603,28 +2603,28 @@
     </row>
     <row r="28" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A28" s="6">
-        <v>43983</v>
+        <v>44013</v>
       </c>
       <c r="B28" s="7">
-        <v>45.2</v>
+        <v>47.9</v>
       </c>
       <c r="C28" s="7">
-        <v>47.9</v>
+        <v>43</v>
       </c>
       <c r="D28" s="7">
-        <v>52.7</v>
+        <v>60.6</v>
       </c>
       <c r="E28" s="7">
-        <v>43.8</v>
+        <v>40.049999999999997</v>
       </c>
       <c r="F28" s="10">
-        <v>2.75</v>
+        <v>-4.9000000000000004</v>
       </c>
       <c r="G28" s="10">
-        <v>6.09</v>
+        <v>-10.23</v>
       </c>
       <c r="H28" s="9">
-        <v>0</v>
+        <v>3.0000000000000001E-3</v>
       </c>
       <c r="I28" s="9" t="s">
         <v>17</v>
@@ -2633,13 +2633,13 @@
         <v>17</v>
       </c>
       <c r="K28" s="9">
-        <v>0</v>
+        <v>3.0000000000000001E-3</v>
       </c>
       <c r="L28" s="9" t="s">
         <v>17</v>
       </c>
       <c r="M28" s="9">
-        <v>0</v>
+        <v>3.0000000000000001E-3</v>
       </c>
       <c r="N28" s="9" t="s">
         <v>17</v>
@@ -2648,7 +2648,7 @@
         <v>17</v>
       </c>
       <c r="P28" s="9">
-        <v>0</v>
+        <v>3.0000000000000001E-3</v>
       </c>
       <c r="Q28" s="9" t="s">
         <v>17</v>
@@ -2656,25 +2656,25 @@
     </row>
     <row r="29" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A29" s="6">
-        <v>43952</v>
+        <v>43983</v>
       </c>
       <c r="B29" s="7">
-        <v>37.5</v>
+        <v>45.2</v>
       </c>
       <c r="C29" s="7">
-        <v>45.15</v>
+        <v>47.9</v>
       </c>
       <c r="D29" s="7">
-        <v>52.8</v>
+        <v>52.7</v>
       </c>
       <c r="E29" s="7">
-        <v>37.450000000000003</v>
-      </c>
-      <c r="F29" s="10">
-        <v>7.1</v>
-      </c>
-      <c r="G29" s="10">
-        <v>18.66</v>
+        <v>43.8</v>
+      </c>
+      <c r="F29" s="8">
+        <v>2.75</v>
+      </c>
+      <c r="G29" s="8">
+        <v>6.09</v>
       </c>
       <c r="H29" s="9">
         <v>0</v>
@@ -2709,25 +2709,25 @@
     </row>
     <row r="30" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A30" s="6">
-        <v>43922</v>
+        <v>43952</v>
       </c>
       <c r="B30" s="7">
-        <v>30.55</v>
+        <v>37.5</v>
       </c>
       <c r="C30" s="7">
-        <v>38.049999999999997</v>
+        <v>45.15</v>
       </c>
       <c r="D30" s="7">
-        <v>39</v>
+        <v>52.8</v>
       </c>
       <c r="E30" s="7">
-        <v>29.9</v>
-      </c>
-      <c r="F30" s="10">
-        <v>7.65</v>
-      </c>
-      <c r="G30" s="10">
-        <v>25.16</v>
+        <v>37.450000000000003</v>
+      </c>
+      <c r="F30" s="8">
+        <v>7.1</v>
+      </c>
+      <c r="G30" s="8">
+        <v>18.66</v>
       </c>
       <c r="H30" s="9">
         <v>0</v>
@@ -2762,25 +2762,25 @@
     </row>
     <row r="31" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A31" s="6">
-        <v>43891</v>
+        <v>43922</v>
       </c>
       <c r="B31" s="7">
-        <v>43.5</v>
+        <v>30.55</v>
       </c>
       <c r="C31" s="7">
-        <v>30.4</v>
+        <v>38.049999999999997</v>
       </c>
       <c r="D31" s="7">
-        <v>48.5</v>
+        <v>39</v>
       </c>
       <c r="E31" s="7">
-        <v>24.5</v>
+        <v>29.9</v>
       </c>
       <c r="F31" s="8">
-        <v>-14.05</v>
+        <v>7.65</v>
       </c>
       <c r="G31" s="8">
-        <v>-31.61</v>
+        <v>25.16</v>
       </c>
       <c r="H31" s="9">
         <v>0</v>
@@ -2815,25 +2815,25 @@
     </row>
     <row r="32" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A32" s="6">
-        <v>43862</v>
+        <v>43891</v>
       </c>
       <c r="B32" s="7">
-        <v>41.9</v>
+        <v>43.5</v>
       </c>
       <c r="C32" s="7">
-        <v>44.45</v>
+        <v>30.4</v>
       </c>
       <c r="D32" s="7">
-        <v>48.85</v>
+        <v>48.5</v>
       </c>
       <c r="E32" s="7">
-        <v>38.75</v>
+        <v>24.5</v>
       </c>
       <c r="F32" s="10">
-        <v>2.7</v>
+        <v>-14.05</v>
       </c>
       <c r="G32" s="10">
-        <v>6.47</v>
+        <v>-31.61</v>
       </c>
       <c r="H32" s="9">
         <v>0</v>
@@ -2868,25 +2868,25 @@
     </row>
     <row r="33" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A33" s="6">
-        <v>43831</v>
+        <v>43862</v>
       </c>
       <c r="B33" s="7">
-        <v>44.5</v>
+        <v>41.9</v>
       </c>
       <c r="C33" s="7">
-        <v>41.75</v>
+        <v>44.45</v>
       </c>
       <c r="D33" s="7">
-        <v>45.1</v>
+        <v>48.85</v>
       </c>
       <c r="E33" s="7">
-        <v>41.3</v>
+        <v>38.75</v>
       </c>
       <c r="F33" s="8">
-        <v>-3</v>
+        <v>2.7</v>
       </c>
       <c r="G33" s="8">
-        <v>-6.7</v>
+        <v>6.47</v>
       </c>
       <c r="H33" s="9">
         <v>0</v>
@@ -2921,25 +2921,25 @@
     </row>
     <row r="34" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A34" s="6">
-        <v>43800</v>
+        <v>43831</v>
       </c>
       <c r="B34" s="7">
-        <v>49.5</v>
+        <v>44.5</v>
       </c>
       <c r="C34" s="7">
-        <v>44.75</v>
+        <v>41.75</v>
       </c>
       <c r="D34" s="7">
-        <v>49.5</v>
+        <v>45.1</v>
       </c>
       <c r="E34" s="7">
-        <v>36.85</v>
-      </c>
-      <c r="F34" s="8">
-        <v>-4.45</v>
-      </c>
-      <c r="G34" s="8">
-        <v>-9.0399999999999991</v>
+        <v>41.3</v>
+      </c>
+      <c r="F34" s="10">
+        <v>-3</v>
+      </c>
+      <c r="G34" s="10">
+        <v>-6.7</v>
       </c>
       <c r="H34" s="9">
         <v>0</v>
@@ -2974,25 +2974,25 @@
     </row>
     <row r="35" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A35" s="6">
-        <v>43770</v>
+        <v>43800</v>
       </c>
       <c r="B35" s="7">
-        <v>51.5</v>
+        <v>49.5</v>
       </c>
       <c r="C35" s="7">
-        <v>49.2</v>
+        <v>44.75</v>
       </c>
       <c r="D35" s="7">
-        <v>53.9</v>
+        <v>49.5</v>
       </c>
       <c r="E35" s="7">
-        <v>47.75</v>
-      </c>
-      <c r="F35" s="8">
-        <v>-2.2999999999999998</v>
-      </c>
-      <c r="G35" s="8">
-        <v>-4.47</v>
+        <v>36.85</v>
+      </c>
+      <c r="F35" s="10">
+        <v>-4.45</v>
+      </c>
+      <c r="G35" s="10">
+        <v>-9.0399999999999991</v>
       </c>
       <c r="H35" s="9">
         <v>0</v>
@@ -3027,25 +3027,25 @@
     </row>
     <row r="36" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A36" s="6">
-        <v>43739</v>
+        <v>43770</v>
       </c>
       <c r="B36" s="7">
-        <v>64.7</v>
+        <v>51.5</v>
       </c>
       <c r="C36" s="7">
-        <v>51.5</v>
+        <v>49.2</v>
       </c>
       <c r="D36" s="7">
-        <v>65.8</v>
+        <v>53.9</v>
       </c>
       <c r="E36" s="7">
-        <v>50.5</v>
-      </c>
-      <c r="F36" s="8">
-        <v>-13.5</v>
-      </c>
-      <c r="G36" s="8">
-        <v>-20.77</v>
+        <v>47.75</v>
+      </c>
+      <c r="F36" s="10">
+        <v>-2.2999999999999998</v>
+      </c>
+      <c r="G36" s="10">
+        <v>-4.47</v>
       </c>
       <c r="H36" s="9">
         <v>0</v>
@@ -3080,25 +3080,25 @@
     </row>
     <row r="37" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A37" s="6">
-        <v>43709</v>
+        <v>43739</v>
       </c>
       <c r="B37" s="7">
-        <v>69.900000000000006</v>
+        <v>64.7</v>
       </c>
       <c r="C37" s="7">
-        <v>65</v>
+        <v>51.5</v>
       </c>
       <c r="D37" s="7">
-        <v>73.5</v>
+        <v>65.8</v>
       </c>
       <c r="E37" s="7">
-        <v>64.3</v>
-      </c>
-      <c r="F37" s="8">
-        <v>-4.3</v>
-      </c>
-      <c r="G37" s="8">
-        <v>-6.2</v>
+        <v>50.5</v>
+      </c>
+      <c r="F37" s="10">
+        <v>-13.5</v>
+      </c>
+      <c r="G37" s="10">
+        <v>-20.77</v>
       </c>
       <c r="H37" s="9">
         <v>0</v>
@@ -3133,25 +3133,25 @@
     </row>
     <row r="38" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A38" s="6">
-        <v>43678</v>
+        <v>43709</v>
       </c>
       <c r="B38" s="7">
-        <v>72</v>
+        <v>69.900000000000006</v>
       </c>
       <c r="C38" s="7">
-        <v>69.3</v>
+        <v>65</v>
       </c>
       <c r="D38" s="7">
-        <v>72.5</v>
+        <v>73.5</v>
       </c>
       <c r="E38" s="7">
-        <v>66.2</v>
-      </c>
-      <c r="F38" s="8">
-        <v>-2.7</v>
-      </c>
-      <c r="G38" s="8">
-        <v>-3.75</v>
+        <v>64.3</v>
+      </c>
+      <c r="F38" s="10">
+        <v>-4.3</v>
+      </c>
+      <c r="G38" s="10">
+        <v>-6.2</v>
       </c>
       <c r="H38" s="9">
         <v>0</v>
@@ -3186,25 +3186,25 @@
     </row>
     <row r="39" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A39" s="6">
-        <v>43647</v>
+        <v>43678</v>
       </c>
       <c r="B39" s="7">
-        <v>74.3</v>
+        <v>72</v>
       </c>
       <c r="C39" s="7">
-        <v>72</v>
+        <v>69.3</v>
       </c>
       <c r="D39" s="7">
-        <v>83.9</v>
+        <v>72.5</v>
       </c>
       <c r="E39" s="7">
-        <v>71</v>
-      </c>
-      <c r="F39" s="8">
-        <v>-1.2</v>
-      </c>
-      <c r="G39" s="8">
-        <v>-1.64</v>
+        <v>66.2</v>
+      </c>
+      <c r="F39" s="10">
+        <v>-2.7</v>
+      </c>
+      <c r="G39" s="10">
+        <v>-3.75</v>
       </c>
       <c r="H39" s="9">
         <v>0</v>
@@ -3239,25 +3239,25 @@
     </row>
     <row r="40" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A40" s="6">
-        <v>43617</v>
+        <v>43647</v>
       </c>
       <c r="B40" s="7">
-        <v>74.2</v>
+        <v>74.3</v>
       </c>
       <c r="C40" s="7">
-        <v>73.2</v>
+        <v>72</v>
       </c>
       <c r="D40" s="7">
-        <v>77.900000000000006</v>
+        <v>83.9</v>
       </c>
       <c r="E40" s="7">
-        <v>72.599999999999994</v>
-      </c>
-      <c r="F40" s="8">
-        <v>-1</v>
-      </c>
-      <c r="G40" s="8">
-        <v>-1.35</v>
+        <v>71</v>
+      </c>
+      <c r="F40" s="10">
+        <v>-1.2</v>
+      </c>
+      <c r="G40" s="10">
+        <v>-1.64</v>
       </c>
       <c r="H40" s="9">
         <v>0</v>
@@ -3292,25 +3292,25 @@
     </row>
     <row r="41" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A41" s="6">
-        <v>43586</v>
+        <v>43617</v>
       </c>
       <c r="B41" s="7">
-        <v>70.599999999999994</v>
+        <v>74.2</v>
       </c>
       <c r="C41" s="7">
-        <v>74.2</v>
+        <v>73.2</v>
       </c>
       <c r="D41" s="7">
-        <v>75.900000000000006</v>
+        <v>77.900000000000006</v>
       </c>
       <c r="E41" s="7">
-        <v>63.4</v>
+        <v>72.599999999999994</v>
       </c>
       <c r="F41" s="10">
-        <v>3.6</v>
+        <v>-1</v>
       </c>
       <c r="G41" s="10">
-        <v>5.0999999999999996</v>
+        <v>-1.35</v>
       </c>
       <c r="H41" s="9">
         <v>0</v>
@@ -3345,25 +3345,25 @@
     </row>
     <row r="42" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A42" s="6">
-        <v>43556</v>
+        <v>43586</v>
       </c>
       <c r="B42" s="7">
-        <v>74.099999999999994</v>
+        <v>70.599999999999994</v>
       </c>
       <c r="C42" s="7">
-        <v>70.599999999999994</v>
+        <v>74.2</v>
       </c>
       <c r="D42" s="7">
-        <v>77.5</v>
+        <v>75.900000000000006</v>
       </c>
       <c r="E42" s="7">
-        <v>70.5</v>
+        <v>63.4</v>
       </c>
       <c r="F42" s="8">
-        <v>-3.3</v>
+        <v>3.6</v>
       </c>
       <c r="G42" s="8">
-        <v>-4.47</v>
+        <v>5.0999999999999996</v>
       </c>
       <c r="H42" s="9">
         <v>0</v>
@@ -3398,25 +3398,25 @@
     </row>
     <row r="43" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A43" s="6">
-        <v>43525</v>
+        <v>43556</v>
       </c>
       <c r="B43" s="7">
-        <v>76.5</v>
+        <v>74.099999999999994</v>
       </c>
       <c r="C43" s="7">
-        <v>73.900000000000006</v>
+        <v>70.599999999999994</v>
       </c>
       <c r="D43" s="7">
-        <v>77.8</v>
+        <v>77.5</v>
       </c>
       <c r="E43" s="7">
         <v>70.5</v>
       </c>
-      <c r="F43" s="8">
-        <v>-1.6</v>
-      </c>
-      <c r="G43" s="8">
-        <v>-2.12</v>
+      <c r="F43" s="10">
+        <v>-3.3</v>
+      </c>
+      <c r="G43" s="10">
+        <v>-4.47</v>
       </c>
       <c r="H43" s="9">
         <v>0</v>
@@ -3451,25 +3451,25 @@
     </row>
     <row r="44" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A44" s="6">
-        <v>43497</v>
+        <v>43525</v>
       </c>
       <c r="B44" s="7">
-        <v>69</v>
+        <v>76.5</v>
       </c>
       <c r="C44" s="7">
-        <v>75.5</v>
+        <v>73.900000000000006</v>
       </c>
       <c r="D44" s="7">
-        <v>80.900000000000006</v>
+        <v>77.8</v>
       </c>
       <c r="E44" s="7">
-        <v>69</v>
+        <v>70.5</v>
       </c>
       <c r="F44" s="10">
-        <v>6.9</v>
+        <v>-1.6</v>
       </c>
       <c r="G44" s="10">
-        <v>10.06</v>
+        <v>-2.12</v>
       </c>
       <c r="H44" s="9">
         <v>0</v>
@@ -3504,25 +3504,25 @@
     </row>
     <row r="45" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A45" s="6">
-        <v>43466</v>
+        <v>43497</v>
       </c>
       <c r="B45" s="7">
-        <v>62.9</v>
+        <v>69</v>
       </c>
       <c r="C45" s="7">
-        <v>68.599999999999994</v>
+        <v>75.5</v>
       </c>
       <c r="D45" s="7">
-        <v>70.900000000000006</v>
+        <v>80.900000000000006</v>
       </c>
       <c r="E45" s="7">
-        <v>61.5</v>
-      </c>
-      <c r="F45" s="10">
-        <v>6.1</v>
-      </c>
-      <c r="G45" s="10">
-        <v>9.76</v>
+        <v>69</v>
+      </c>
+      <c r="F45" s="8">
+        <v>6.9</v>
+      </c>
+      <c r="G45" s="8">
+        <v>10.06</v>
       </c>
       <c r="H45" s="9">
         <v>0</v>
@@ -3557,25 +3557,25 @@
     </row>
     <row r="46" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A46" s="6">
-        <v>43435</v>
+        <v>43466</v>
       </c>
       <c r="B46" s="7">
-        <v>65.8</v>
+        <v>62.9</v>
       </c>
       <c r="C46" s="7">
-        <v>62.5</v>
+        <v>68.599999999999994</v>
       </c>
       <c r="D46" s="7">
-        <v>66.5</v>
+        <v>70.900000000000006</v>
       </c>
       <c r="E46" s="7">
-        <v>59</v>
+        <v>61.5</v>
       </c>
       <c r="F46" s="8">
-        <v>-2.2000000000000002</v>
+        <v>6.1</v>
       </c>
       <c r="G46" s="8">
-        <v>-3.4</v>
+        <v>9.76</v>
       </c>
       <c r="H46" s="9">
         <v>0</v>
@@ -3610,25 +3610,25 @@
     </row>
     <row r="47" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A47" s="6">
-        <v>43405</v>
+        <v>43435</v>
       </c>
       <c r="B47" s="7">
-        <v>56</v>
+        <v>65.8</v>
       </c>
       <c r="C47" s="7">
-        <v>64.7</v>
+        <v>62.5</v>
       </c>
       <c r="D47" s="7">
-        <v>66.400000000000006</v>
+        <v>66.5</v>
       </c>
       <c r="E47" s="7">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="F47" s="10">
-        <v>8.6999999999999993</v>
+        <v>-2.2000000000000002</v>
       </c>
       <c r="G47" s="10">
-        <v>15.54</v>
+        <v>-3.4</v>
       </c>
       <c r="H47" s="9">
         <v>0</v>
@@ -3663,25 +3663,25 @@
     </row>
     <row r="48" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A48" s="6">
-        <v>43374</v>
+        <v>43405</v>
       </c>
       <c r="B48" s="7">
-        <v>83.4</v>
+        <v>56</v>
       </c>
       <c r="C48" s="7">
-        <v>56</v>
+        <v>64.7</v>
       </c>
       <c r="D48" s="7">
-        <v>84.9</v>
+        <v>66.400000000000006</v>
       </c>
       <c r="E48" s="7">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="F48" s="8">
-        <v>-22</v>
+        <v>8.6999999999999993</v>
       </c>
       <c r="G48" s="8">
-        <v>-28.21</v>
+        <v>15.54</v>
       </c>
       <c r="H48" s="9">
         <v>0</v>
@@ -3716,25 +3716,25 @@
     </row>
     <row r="49" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A49" s="6">
-        <v>43344</v>
+        <v>43374</v>
       </c>
       <c r="B49" s="7">
-        <v>84.6</v>
+        <v>83.4</v>
       </c>
       <c r="C49" s="7">
-        <v>78</v>
+        <v>56</v>
       </c>
       <c r="D49" s="7">
-        <v>84.6</v>
+        <v>84.9</v>
       </c>
       <c r="E49" s="7">
-        <v>72.900000000000006</v>
-      </c>
-      <c r="F49" s="8">
-        <v>-6</v>
-      </c>
-      <c r="G49" s="8">
-        <v>-7.14</v>
+        <v>53</v>
+      </c>
+      <c r="F49" s="10">
+        <v>-22</v>
+      </c>
+      <c r="G49" s="10">
+        <v>-28.21</v>
       </c>
       <c r="H49" s="9">
         <v>0</v>
@@ -3769,25 +3769,25 @@
     </row>
     <row r="50" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A50" s="6">
-        <v>43313</v>
+        <v>43344</v>
       </c>
       <c r="B50" s="7">
-        <v>89</v>
+        <v>84.6</v>
       </c>
       <c r="C50" s="7">
-        <v>84</v>
+        <v>78</v>
       </c>
       <c r="D50" s="7">
-        <v>90.5</v>
+        <v>84.6</v>
       </c>
       <c r="E50" s="7">
-        <v>82.7</v>
-      </c>
-      <c r="F50" s="8">
-        <v>-4.5</v>
-      </c>
-      <c r="G50" s="8">
-        <v>-5.08</v>
+        <v>72.900000000000006</v>
+      </c>
+      <c r="F50" s="10">
+        <v>-6</v>
+      </c>
+      <c r="G50" s="10">
+        <v>-7.14</v>
       </c>
       <c r="H50" s="9">
         <v>0</v>
@@ -3822,25 +3822,25 @@
     </row>
     <row r="51" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A51" s="6">
-        <v>43282</v>
+        <v>43313</v>
       </c>
       <c r="B51" s="7">
-        <v>102</v>
+        <v>89</v>
       </c>
       <c r="C51" s="7">
-        <v>88.5</v>
+        <v>84</v>
       </c>
       <c r="D51" s="7">
-        <v>103</v>
+        <v>90.5</v>
       </c>
       <c r="E51" s="7">
-        <v>87.5</v>
-      </c>
-      <c r="F51" s="8">
-        <v>-14</v>
-      </c>
-      <c r="G51" s="8">
-        <v>-13.66</v>
+        <v>82.7</v>
+      </c>
+      <c r="F51" s="10">
+        <v>-4.5</v>
+      </c>
+      <c r="G51" s="10">
+        <v>-5.08</v>
       </c>
       <c r="H51" s="9">
         <v>0</v>
@@ -3875,25 +3875,25 @@
     </row>
     <row r="52" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A52" s="6">
-        <v>43252</v>
+        <v>43282</v>
       </c>
       <c r="B52" s="7">
-        <v>113.5</v>
+        <v>102</v>
       </c>
       <c r="C52" s="7">
-        <v>102.5</v>
+        <v>88.5</v>
       </c>
       <c r="D52" s="7">
-        <v>113.5</v>
+        <v>103</v>
       </c>
       <c r="E52" s="7">
-        <v>97.6</v>
-      </c>
-      <c r="F52" s="8">
-        <v>-9</v>
-      </c>
-      <c r="G52" s="8">
-        <v>-8.07</v>
+        <v>87.5</v>
+      </c>
+      <c r="F52" s="10">
+        <v>-14</v>
+      </c>
+      <c r="G52" s="10">
+        <v>-13.66</v>
       </c>
       <c r="H52" s="9">
         <v>0</v>
@@ -3928,25 +3928,25 @@
     </row>
     <row r="53" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A53" s="6">
-        <v>43221</v>
+        <v>43252</v>
       </c>
       <c r="B53" s="7">
-        <v>115</v>
+        <v>113.5</v>
       </c>
       <c r="C53" s="7">
-        <v>111.5</v>
+        <v>102.5</v>
       </c>
       <c r="D53" s="7">
-        <v>132.5</v>
+        <v>113.5</v>
       </c>
       <c r="E53" s="7">
-        <v>108.5</v>
-      </c>
-      <c r="F53" s="8">
-        <v>-2.5</v>
-      </c>
-      <c r="G53" s="8">
-        <v>-2.19</v>
+        <v>97.6</v>
+      </c>
+      <c r="F53" s="10">
+        <v>-9</v>
+      </c>
+      <c r="G53" s="10">
+        <v>-8.07</v>
       </c>
       <c r="H53" s="9">
         <v>0</v>
@@ -3981,25 +3981,25 @@
     </row>
     <row r="54" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A54" s="6">
-        <v>43191</v>
+        <v>43221</v>
       </c>
       <c r="B54" s="7">
-        <v>103</v>
+        <v>115</v>
       </c>
       <c r="C54" s="7">
-        <v>114</v>
+        <v>111.5</v>
       </c>
       <c r="D54" s="7">
-        <v>120</v>
+        <v>132.5</v>
       </c>
       <c r="E54" s="7">
-        <v>97.6</v>
+        <v>108.5</v>
       </c>
       <c r="F54" s="10">
-        <v>11</v>
+        <v>-2.5</v>
       </c>
       <c r="G54" s="10">
-        <v>10.68</v>
+        <v>-2.19</v>
       </c>
       <c r="H54" s="9">
         <v>0</v>
@@ -4034,25 +4034,25 @@
     </row>
     <row r="55" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A55" s="6">
-        <v>43160</v>
+        <v>43191</v>
       </c>
       <c r="B55" s="7">
-        <v>83</v>
+        <v>103</v>
       </c>
       <c r="C55" s="7">
-        <v>103</v>
+        <v>114</v>
       </c>
       <c r="D55" s="7">
-        <v>115</v>
+        <v>120</v>
       </c>
       <c r="E55" s="7">
-        <v>79.099999999999994</v>
-      </c>
-      <c r="F55" s="10">
-        <v>19.3</v>
-      </c>
-      <c r="G55" s="10">
-        <v>23.06</v>
+        <v>97.6</v>
+      </c>
+      <c r="F55" s="8">
+        <v>11</v>
+      </c>
+      <c r="G55" s="8">
+        <v>10.68</v>
       </c>
       <c r="H55" s="9">
         <v>0</v>
@@ -4087,25 +4087,25 @@
     </row>
     <row r="56" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A56" s="6">
-        <v>43132</v>
+        <v>43160</v>
       </c>
       <c r="B56" s="7">
-        <v>86.5</v>
+        <v>83</v>
       </c>
       <c r="C56" s="7">
-        <v>83.7</v>
+        <v>103</v>
       </c>
       <c r="D56" s="7">
-        <v>87.3</v>
+        <v>115</v>
       </c>
       <c r="E56" s="7">
-        <v>78.3</v>
+        <v>79.099999999999994</v>
       </c>
       <c r="F56" s="8">
-        <v>-3.3</v>
+        <v>19.3</v>
       </c>
       <c r="G56" s="8">
-        <v>-3.79</v>
+        <v>23.06</v>
       </c>
       <c r="H56" s="9">
         <v>0</v>
@@ -4140,25 +4140,25 @@
     </row>
     <row r="57" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A57" s="6">
-        <v>43101</v>
+        <v>43132</v>
       </c>
       <c r="B57" s="7">
-        <v>75.099999999999994</v>
+        <v>86.5</v>
       </c>
       <c r="C57" s="7">
-        <v>87</v>
+        <v>83.7</v>
       </c>
       <c r="D57" s="7">
-        <v>90.5</v>
+        <v>87.3</v>
       </c>
       <c r="E57" s="7">
-        <v>72.2</v>
+        <v>78.3</v>
       </c>
       <c r="F57" s="10">
-        <v>11.3</v>
+        <v>-3.3</v>
       </c>
       <c r="G57" s="10">
-        <v>14.93</v>
+        <v>-3.79</v>
       </c>
       <c r="H57" s="9">
         <v>0</v>
@@ -4193,25 +4193,25 @@
     </row>
     <row r="58" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A58" s="6">
-        <v>43070</v>
+        <v>43101</v>
       </c>
       <c r="B58" s="7">
-        <v>84</v>
+        <v>75.099999999999994</v>
       </c>
       <c r="C58" s="7">
-        <v>75.7</v>
+        <v>87</v>
       </c>
       <c r="D58" s="7">
-        <v>84</v>
+        <v>90.5</v>
       </c>
       <c r="E58" s="7">
-        <v>73.5</v>
+        <v>72.2</v>
       </c>
       <c r="F58" s="8">
-        <v>-8.4</v>
+        <v>11.3</v>
       </c>
       <c r="G58" s="8">
-        <v>-9.99</v>
+        <v>14.93</v>
       </c>
       <c r="H58" s="9">
         <v>0</v>
@@ -4246,25 +4246,25 @@
     </row>
     <row r="59" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A59" s="6">
-        <v>43040</v>
+        <v>43070</v>
       </c>
       <c r="B59" s="7">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="C59" s="7">
-        <v>84.1</v>
+        <v>75.7</v>
       </c>
       <c r="D59" s="7">
-        <v>89.7</v>
+        <v>84</v>
       </c>
       <c r="E59" s="7">
-        <v>81.400000000000006</v>
-      </c>
-      <c r="F59" s="8">
-        <v>-3.2</v>
-      </c>
-      <c r="G59" s="8">
-        <v>-3.67</v>
+        <v>73.5</v>
+      </c>
+      <c r="F59" s="10">
+        <v>-8.4</v>
+      </c>
+      <c r="G59" s="10">
+        <v>-9.99</v>
       </c>
       <c r="H59" s="9">
         <v>0</v>
@@ -4299,25 +4299,25 @@
     </row>
     <row r="60" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A60" s="6">
-        <v>43009</v>
+        <v>43040</v>
       </c>
       <c r="B60" s="7">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="C60" s="7">
-        <v>87.3</v>
+        <v>84.1</v>
       </c>
       <c r="D60" s="7">
-        <v>101.5</v>
+        <v>89.7</v>
       </c>
       <c r="E60" s="7">
-        <v>81</v>
+        <v>81.400000000000006</v>
       </c>
       <c r="F60" s="10">
-        <v>15.3</v>
+        <v>-3.2</v>
       </c>
       <c r="G60" s="10">
-        <v>21.25</v>
+        <v>-3.67</v>
       </c>
       <c r="H60" s="9">
         <v>0</v>
@@ -4352,25 +4352,25 @@
     </row>
     <row r="61" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A61" s="6">
-        <v>42979</v>
-      </c>
-      <c r="B61" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="C61" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="D61" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="E61" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="F61" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="G61" s="9" t="s">
-        <v>17</v>
+        <v>43009</v>
+      </c>
+      <c r="B61" s="7">
+        <v>83</v>
+      </c>
+      <c r="C61" s="7">
+        <v>87.3</v>
+      </c>
+      <c r="D61" s="7">
+        <v>101.5</v>
+      </c>
+      <c r="E61" s="7">
+        <v>81</v>
+      </c>
+      <c r="F61" s="8">
+        <v>15.3</v>
+      </c>
+      <c r="G61" s="8">
+        <v>21.25</v>
       </c>
       <c r="H61" s="9">
         <v>0</v>
@@ -4405,7 +4405,7 @@
     </row>
     <row r="62" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A62" s="6">
-        <v>42948</v>
+        <v>42979</v>
       </c>
       <c r="B62" s="7" t="s">
         <v>17</v>
@@ -4458,7 +4458,7 @@
     </row>
     <row r="63" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A63" s="6">
-        <v>42917</v>
+        <v>42948</v>
       </c>
       <c r="B63" s="7" t="s">
         <v>17</v>
@@ -4511,7 +4511,7 @@
     </row>
     <row r="64" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A64" s="6">
-        <v>42887</v>
+        <v>42917</v>
       </c>
       <c r="B64" s="7" t="s">
         <v>17</v>
@@ -4564,7 +4564,7 @@
     </row>
     <row r="65" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A65" s="6">
-        <v>42856</v>
+        <v>42887</v>
       </c>
       <c r="B65" s="7" t="s">
         <v>17</v>
@@ -4617,7 +4617,7 @@
     </row>
     <row r="66" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A66" s="6">
-        <v>42826</v>
+        <v>42856</v>
       </c>
       <c r="B66" s="7" t="s">
         <v>17</v>
@@ -4670,7 +4670,7 @@
     </row>
     <row r="67" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A67" s="6">
-        <v>42795</v>
+        <v>42826</v>
       </c>
       <c r="B67" s="7" t="s">
         <v>17</v>
@@ -4723,7 +4723,7 @@
     </row>
     <row r="68" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A68" s="6">
-        <v>42767</v>
+        <v>42795</v>
       </c>
       <c r="B68" s="7" t="s">
         <v>17</v>
@@ -4776,7 +4776,7 @@
     </row>
     <row r="69" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A69" s="6">
-        <v>42736</v>
+        <v>42767</v>
       </c>
       <c r="B69" s="7" t="s">
         <v>17</v>
@@ -4829,7 +4829,7 @@
     </row>
     <row r="70" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A70" s="6">
-        <v>42705</v>
+        <v>42736</v>
       </c>
       <c r="B70" s="7" t="s">
         <v>17</v>
@@ -4882,7 +4882,7 @@
     </row>
     <row r="71" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A71" s="6">
-        <v>42675</v>
+        <v>42705</v>
       </c>
       <c r="B71" s="7" t="s">
         <v>17</v>
@@ -4935,7 +4935,7 @@
     </row>
     <row r="72" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A72" s="6">
-        <v>42644</v>
+        <v>42675</v>
       </c>
       <c r="B72" s="7" t="s">
         <v>17</v>
@@ -4988,7 +4988,7 @@
     </row>
     <row r="73" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A73" s="6">
-        <v>42614</v>
+        <v>42644</v>
       </c>
       <c r="B73" s="7" t="s">
         <v>17</v>
@@ -5041,7 +5041,7 @@
     </row>
     <row r="74" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A74" s="6">
-        <v>42583</v>
+        <v>42614</v>
       </c>
       <c r="B74" s="7" t="s">
         <v>17</v>
@@ -5094,7 +5094,7 @@
     </row>
     <row r="75" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A75" s="6">
-        <v>42552</v>
+        <v>42583</v>
       </c>
       <c r="B75" s="7" t="s">
         <v>17</v>
@@ -5147,7 +5147,7 @@
     </row>
     <row r="76" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A76" s="6">
-        <v>42522</v>
+        <v>42552</v>
       </c>
       <c r="B76" s="7" t="s">
         <v>17</v>
@@ -5200,7 +5200,7 @@
     </row>
     <row r="77" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A77" s="6">
-        <v>42491</v>
+        <v>42522</v>
       </c>
       <c r="B77" s="7" t="s">
         <v>17</v>
@@ -5253,7 +5253,7 @@
     </row>
     <row r="78" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A78" s="6">
-        <v>42461</v>
+        <v>42491</v>
       </c>
       <c r="B78" s="7" t="s">
         <v>17</v>
@@ -5306,7 +5306,7 @@
     </row>
     <row r="79" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A79" s="6">
-        <v>42430</v>
+        <v>42461</v>
       </c>
       <c r="B79" s="7" t="s">
         <v>17</v>
@@ -5359,7 +5359,7 @@
     </row>
     <row r="80" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A80" s="6">
-        <v>42401</v>
+        <v>42430</v>
       </c>
       <c r="B80" s="7" t="s">
         <v>17</v>
@@ -5412,7 +5412,7 @@
     </row>
     <row r="81" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A81" s="6">
-        <v>42370</v>
+        <v>42401</v>
       </c>
       <c r="B81" s="7" t="s">
         <v>17</v>
@@ -5465,7 +5465,7 @@
     </row>
     <row r="82" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A82" s="6">
-        <v>42339</v>
+        <v>42370</v>
       </c>
       <c r="B82" s="7" t="s">
         <v>17</v>
@@ -5518,7 +5518,7 @@
     </row>
     <row r="83" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A83" s="6">
-        <v>42309</v>
+        <v>42339</v>
       </c>
       <c r="B83" s="7" t="s">
         <v>17</v>
@@ -5571,7 +5571,7 @@
     </row>
     <row r="84" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A84" s="6">
-        <v>42278</v>
+        <v>42309</v>
       </c>
       <c r="B84" s="7" t="s">
         <v>17</v>
@@ -5624,7 +5624,7 @@
     </row>
     <row r="85" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A85" s="6">
-        <v>42248</v>
+        <v>42278</v>
       </c>
       <c r="B85" s="7" t="s">
         <v>17</v>
@@ -5677,7 +5677,7 @@
     </row>
     <row r="86" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A86" s="6">
-        <v>42217</v>
+        <v>42248</v>
       </c>
       <c r="B86" s="7" t="s">
         <v>17</v>
@@ -5730,54 +5730,107 @@
     </row>
     <row r="87" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A87" s="6">
+        <v>42217</v>
+      </c>
+      <c r="B87" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="C87" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="D87" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="E87" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="F87" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="G87" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="H87" s="9">
+        <v>0</v>
+      </c>
+      <c r="I87" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="J87" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="K87" s="9">
+        <v>0</v>
+      </c>
+      <c r="L87" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="M87" s="9">
+        <v>0</v>
+      </c>
+      <c r="N87" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="O87" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="P87" s="9">
+        <v>0</v>
+      </c>
+      <c r="Q87" s="9" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="88" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+      <c r="A88" s="6">
         <v>42186</v>
       </c>
-      <c r="B87" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="C87" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="D87" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="E87" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="F87" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="G87" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="H87" s="9">
-        <v>0</v>
-      </c>
-      <c r="I87" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="J87" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="K87" s="9">
-        <v>0</v>
-      </c>
-      <c r="L87" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="M87" s="9">
-        <v>0</v>
-      </c>
-      <c r="N87" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="O87" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="P87" s="9">
-        <v>0</v>
-      </c>
-      <c r="Q87" s="9" t="s">
+      <c r="B88" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="C88" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="D88" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="E88" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="F88" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="G88" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="H88" s="9">
+        <v>0</v>
+      </c>
+      <c r="I88" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="J88" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="K88" s="9">
+        <v>0</v>
+      </c>
+      <c r="L88" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="M88" s="9">
+        <v>0</v>
+      </c>
+      <c r="N88" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="O88" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="P88" s="9">
+        <v>0</v>
+      </c>
+      <c r="Q88" s="9" t="s">
         <v>17</v>
       </c>
     </row>
